--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-020_上長の部下一覧_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-020_上長の部下一覧_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="9877425"/>
+    <ext cx="8572500" cy="10077450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-020 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-020 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1903,7 +1903,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：共通基盤（@EnableMethodSecurity・AccessDenied / 型不一致ハンドラ）の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：共通基盤（@EnableMethodSecurity・AccessDenied / 型不一致ハンドラ）の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3416,7 +3417,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Long managerId = Long.valueOf(jwt.getSubject())。上長 ID はクエリ・パスから受け取らない（他人の部下を指定できない構造）</t>
+          <t>Long managerId = Long.valueOf(auth.getName())。上長 ID はクエリ・パスから受け取らない（他人の部下を指定できない構造）</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3610,7 +3611,7 @@
           <t>@GetMapping("/subordinates/summary")
 public SubordinateSummaryResponse subordinatesSummary(
     @RequestParam(required = false) String month,
-    @AuthenticationPrincipal Jwt jwt)</t>
+    Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3694,17 +3695,17 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>@AuthenticationPrincipal。sub = ログイン上長の users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -3752,7 +3753,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Long managerId = Long.valueOf(jwt.getSubject());          // ③
+          <t>Long managerId = Long.valueOf(auth.getName());          // ③
 return reportService.subordinates(managerId, month);       // ④〜⑦</t>
         </is>
       </c>
